--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -938,6 +938,216 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,69 +956,69 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -1040,69 +1040,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1086,63 +1086,21 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>115</v>
+        <v>372</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07 12:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>372</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2026-07-07 12:57</t>
         </is>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1106,48 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 19:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,27 +956,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>627</v>
+        <v>735</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -998,11 +998,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1040,27 +1040,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1082,27 +1082,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>372</v>
+        <v>117</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>216</v>
+        <v>402</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 19:26</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,27 +956,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -998,11 +998,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -1082,27 +1082,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>402</v>
+        <v>543</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -938,216 +938,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Academias</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>747</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>543</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -938,6 +938,216 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,69 +956,69 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>751</v>
+        <v>949</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3" t="n">
+      <c r="G13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -1040,69 +1040,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>364</v>
+        <v>445</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="I14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>545</v>
+        <v>597</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,27 +956,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>949</v>
+        <v>1231</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -998,27 +998,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -1040,27 +1040,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>445</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -1082,27 +1082,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>597</v>
+        <v>746</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -956,27 +956,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1231</v>
+        <v>1269</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -998,11 +998,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -1011,14 +1011,14 @@
         <v>49</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>4</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -1040,27 +1040,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>87</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -1124,27 +1124,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>64</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,216 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>548</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>777</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,69 +1166,69 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1300</v>
+        <v>1842</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>139</v>
+        <v>321</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="F18" s="2" t="n">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I18" s="2" t="n">
+      <c r="H18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1250,69 +1250,69 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>548</v>
+        <v>644</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="I20" s="2" t="n">
+      <c r="H20" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="I20" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>777</v>
+        <v>1014</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1842</v>
+        <v>2070</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1208,11 +1208,11 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>1</v>
@@ -1221,14 +1221,14 @@
         <v>49</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>644</v>
+        <v>770</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1292,27 +1292,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1014</v>
+        <v>1128</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2070</v>
+        <v>2230</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1208,27 +1208,27 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>770</v>
+        <v>909</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1292,27 +1292,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1128</v>
+        <v>1213</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2230</v>
+        <v>2832</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>415</v>
+        <v>726</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1208,11 +1208,11 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>1</v>
@@ -1221,14 +1221,14 @@
         <v>59</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>909</v>
+        <v>979</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1292,27 +1292,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>301</v>
+        <v>450</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1213</v>
+        <v>1371</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2832</v>
+        <v>3118</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>726</v>
+        <v>831</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -1221,14 +1221,14 @@
         <v>59</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>979</v>
+        <v>997</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1292,27 +1292,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1371</v>
+        <v>1412</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3118</v>
+        <v>3187</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>831</v>
+        <v>856</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>12</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -1218,17 +1218,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>997</v>
+        <v>1021</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1292,27 +1292,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>9</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1412</v>
+        <v>1428</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>121</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1358,6 +1358,216 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3225</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>554</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,69 +1376,69 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3225</v>
+        <v>3376</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="H23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1460,69 +1460,69 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>554</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>577</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1445</v>
+        <v>1477</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,27 +1376,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3376</v>
+        <v>3549</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>893</v>
+        <v>942</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1418,27 +1418,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>25</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1055</v>
+        <v>1134</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1502,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>51</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1477</v>
+        <v>1511</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,27 +1376,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3549</v>
+        <v>3637</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>942</v>
+        <v>959</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
@@ -1431,14 +1431,14 @@
         <v>61</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1134</v>
+        <v>1301</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1502,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>104</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1511</v>
+        <v>1616</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,27 +1376,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3637</v>
+        <v>3778</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>959</v>
+        <v>1005</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
@@ -1431,14 +1431,14 @@
         <v>61</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1301</v>
+        <v>1540</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1502,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1616</v>
+        <v>1662</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,27 +1376,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3778</v>
+        <v>3876</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1418,27 +1418,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1540</v>
+        <v>1572</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1502,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1662</v>
+        <v>1758</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>147</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1376,27 +1376,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3876</v>
+        <v>3984</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>4</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1572</v>
+        <v>1586</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1502,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1758</v>
+        <v>1775</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>147</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>18</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1568,6 +1568,216 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4058</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>377</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1023</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1605</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>458</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1789</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1586,69 +1586,69 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4058</v>
+        <v>4179</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>377</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1023</v>
+        <v>1095</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I28" s="2" t="n">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="G28" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1670,69 +1670,69 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1605</v>
+        <v>1644</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>751</v>
-      </c>
-      <c r="F30" s="2" t="n">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>755</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="I30" s="2" t="n">
+      <c r="G30" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1789</v>
+        <v>2113</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>243</v>
+        <v>705</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1586,27 +1586,27 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4179</v>
+        <v>5416</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>377</v>
+        <v>456</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1095</v>
+        <v>1267</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1628,27 +1628,27 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>76</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1670,27 +1670,27 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1644</v>
+        <v>2047</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>461</v>
+        <v>581</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>327</v>
+        <v>530</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1712,27 +1712,27 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2113</v>
+        <v>2311</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1586,27 +1586,27 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5416</v>
+        <v>5691</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1267</v>
+        <v>1303</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>8</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1670,27 +1670,27 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2047</v>
+        <v>2140</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1712,27 +1712,27 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2311</v>
+        <v>2336</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1586,27 +1586,27 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5691</v>
+        <v>6016</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1303</v>
+        <v>1406</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>8</v>
@@ -1641,14 +1641,14 @@
         <v>76</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1670,27 +1670,27 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2140</v>
+        <v>2247</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>493</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1712,27 +1712,27 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>781</v>
+        <v>895</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2336</v>
+        <v>2434</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>728</v>
+        <v>872</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1581,32 +1581,32 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6016</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1406</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1623,32 +1623,32 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1665,32 +1665,32 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2247</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1707,32 +1707,32 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2434</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -1641,14 +1641,14 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -1683,14 +1683,14 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -1725,14 +1725,14 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -1767,14 +1767,14 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1778,6 +1778,216 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,69 +1796,69 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1880,69 +1880,69 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,27 +1796,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>753</v>
+        <v>958</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1922,27 +1922,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,27 +1796,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>958</v>
+        <v>1028</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1922,27 +1922,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H36" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,27 +1796,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1028</v>
+        <v>1239</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>117</v>
+        <v>312</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1922,11 +1922,11 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>3</v>
@@ -1935,14 +1935,14 @@
         <v>4</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>201</v>
+        <v>325</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,27 +1796,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1239</v>
+        <v>1336</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>101</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>312</v>
+        <v>417</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1922,27 +1922,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="H36" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -1796,27 +1796,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1336</v>
+        <v>1376</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1838,11 +1838,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>5</v>
@@ -1851,14 +1851,14 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1922,27 +1922,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1964,27 +1964,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1988,6 +1988,216 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1477</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>497</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>660</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,69 +2006,69 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1477</v>
+        <v>1529</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="H37" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="I37" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>S33/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I38" s="2" t="n">
+      <c r="G38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -2090,69 +2090,69 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>52</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>S33/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="F40" s="2" t="n">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="I40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>660</v>
+        <v>786</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,27 +2006,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1529</v>
+        <v>1545</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -2048,11 +2048,11 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>5</v>
@@ -2061,14 +2061,14 @@
         <v>16</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>547</v>
+        <v>687</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -2132,27 +2132,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>786</v>
+        <v>888</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,27 +2006,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1545</v>
+        <v>1648</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -2048,27 +2048,27 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>687</v>
+        <v>1222</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>107</v>
+        <v>263</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -2132,27 +2132,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>888</v>
+        <v>1024</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,27 +2006,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1648</v>
+        <v>1705</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -2048,27 +2048,27 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1222</v>
+        <v>1654</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -2132,27 +2132,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1024</v>
+        <v>1077</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,27 +2006,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1705</v>
+        <v>1765</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -2048,27 +2048,27 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1654</v>
+        <v>1780</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -2132,27 +2132,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2006,27 +2006,27 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1765</v>
+        <v>1792</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>142</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>10</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -2048,11 +2048,11 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>6</v>
@@ -2061,14 +2061,14 @@
         <v>19</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1780</v>
+        <v>1822</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>49</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -2174,27 +2174,27 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1109</v>
+        <v>1123</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2198,216 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1811</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>356</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,69 +2216,69 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1811</v>
+        <v>1938</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="F43" s="3" t="n">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -2300,69 +2300,69 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1840</v>
+        <v>1874</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>356</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>737</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1134</v>
+        <v>1208</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>62</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1938</v>
+        <v>1971</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2258,11 +2258,11 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2300,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1874</v>
+        <v>1975</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2342,27 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>737</v>
+        <v>858</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1208</v>
+        <v>1269</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,11 +2216,11 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>149</v>
@@ -2229,14 +2229,14 @@
         <v>358</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2258,11 +2258,11 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>6</v>
@@ -2271,14 +2271,14 @@
         <v>19</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2300,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1975</v>
+        <v>2077</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2342,27 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>858</v>
+        <v>895</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1982</v>
+        <v>2117</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2258,27 +2258,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="I43" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2300,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2077</v>
+        <v>2109</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2342,27 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>895</v>
+        <v>990</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>72</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1294</v>
+        <v>1337</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2117</v>
+        <v>2144</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>152</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2258,27 +2258,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2300,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2109</v>
+        <v>2138</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2342,17 +2342,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>990</v>
+        <v>1016</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>72</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1337</v>
+        <v>1384</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2144</v>
+        <v>2159</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>152</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2258,11 +2258,11 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>17</v>
@@ -2271,14 +2271,14 @@
         <v>28</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2300,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2138</v>
+        <v>2159</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2342,27 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1384</v>
+        <v>1402</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2408,6 +2408,216 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2164</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>369</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2178</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,69 +2426,69 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2164</v>
+        <v>2254</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>152</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="F48" s="2" t="n">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="F48" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2" t="n">
+      <c r="H48" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -2510,69 +2510,69 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2178</v>
+        <v>2251</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>1041</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>311</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1410</v>
+        <v>1636</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,27 +2426,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2254</v>
+        <v>2281</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>152</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -2478,7 +2478,7 @@
         <v>17</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>32</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2251</v>
+        <v>2287</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2552,27 +2552,27 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>12</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1636</v>
+        <v>1699</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,27 +2426,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2281</v>
+        <v>2477</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2287</v>
+        <v>2305</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2552,27 +2552,27 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1083</v>
+        <v>1433</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1699</v>
+        <v>1717</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>270</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,27 +2426,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2477</v>
+        <v>2495</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>15</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2468,11 +2468,11 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>17</v>
@@ -2481,14 +2481,14 @@
         <v>30</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2552,27 +2552,27 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1433</v>
+        <v>1405</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1717</v>
+        <v>2048</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,27 +2426,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2495</v>
+        <v>2506</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>15</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>349</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2552,27 +2552,27 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2048</v>
+        <v>2071</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2426,27 +2426,27 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2506</v>
+        <v>2523</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>15</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2311</v>
+        <v>2320</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>349</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2552,27 +2552,27 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
         <v>1408</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>365</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2594,27 +2594,27 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2071</v>
+        <v>2088</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2618,6 +2618,216 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2549</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>2324</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1414</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>2101</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2631,74 +2631,74 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2549</v>
+        <v>188</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>444</v>
+        <v>14</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2715,74 +2715,74 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2324</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>1414</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2799,32 +2799,32 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2636,27 +2636,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>188</v>
+        <v>333</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
         <v>14</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="I52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2691,14 +2691,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
@@ -2733,14 +2733,14 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
@@ -2775,14 +2775,14 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
@@ -2817,14 +2817,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2636,27 +2636,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>333</v>
+        <v>466</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2720,27 +2720,27 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2762,27 +2762,27 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2636,27 +2636,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>466</v>
+        <v>556</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2691,14 +2691,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2720,11 +2720,11 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>2</v>
@@ -2733,14 +2733,14 @@
         <v>4</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2762,27 +2762,27 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>289</v>
+        <v>366</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -2817,14 +2817,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2636,27 +2636,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2691,14 +2691,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2720,27 +2720,27 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2762,27 +2762,27 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -2817,14 +2817,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2720,11 +2720,11 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>4</v>
@@ -2733,14 +2733,14 @@
         <v>6</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2828,6 +2828,216 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,49 +2866,49 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,49 +2950,49 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
